--- a/02_HRvLR_groups/05_Module_Preservation/c_data/module_preservation.xlsx
+++ b/02_HRvLR_groups/05_Module_Preservation/c_data/module_preservation.xlsx
@@ -124,7 +124,7 @@
     <t>arm</t>
   </si>
   <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster arc.</t>
+    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
   </si>
   <si>
     <t>n_samples</t>
@@ -5965,7 +5965,7 @@
     <t>corrected</t>
   </si>
   <si>
-    <t>01_Trunk/03_Quantification/c_data/DAList_corrected.rds</t>
+    <t>01_Processing/03_Quantification/c_data/DAList_corrected.rds</t>
   </si>
   <si>
     <t>4b7147a39661ba7f9ed17b81a9ef9a9b</t>
@@ -5974,7 +5974,7 @@
     <t>modules</t>
   </si>
   <si>
-    <t>01_Trunk/06_Module_Building/c_data/modules.rds</t>
+    <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
   </si>
   <si>
     <t>9062a97ff96fac52908895e0eeb7bf57</t>
